--- a/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="269">
   <si>
     <t>Property</t>
   </si>
@@ -395,16 +395,13 @@
     <t>Bundle.type</t>
   </si>
   <si>
-    <t>document | message | transaction | transaction-response | batch | batch-response | history | searchset | collection</t>
+    <t>batch</t>
   </si>
   <si>
     <t>Indicates the purpose of this bundle - how it is intended to be used.</t>
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
-  </si>
-  <si>
-    <t>batch</t>
   </si>
   <si>
     <t>required</t>
@@ -604,7 +601,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>URI for resource (Absolute URL server address or URI for UUID/OID)</t>
+    <t>Uniqe id is mandatory for reference in response</t>
   </si>
   <si>
     <t>All observations must be identified by unique uri by the responsible organization</t>
@@ -709,7 +706,7 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+    <t>POST | PUT</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
@@ -2058,28 +2055,28 @@
         <v>78</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X8" t="s" s="2">
+      <c r="Y8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
@@ -2121,15 +2118,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2152,16 +2149,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2211,7 +2208,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2232,18 +2229,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2266,16 +2263,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2325,7 +2322,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2334,7 +2331,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2354,10 +2351,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2380,16 +2377,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2439,7 +2436,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2468,10 +2465,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2494,13 +2491,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2551,25 +2548,25 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2580,14 +2577,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2606,16 +2603,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2665,7 +2662,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2677,13 +2674,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2694,14 +2691,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2720,19 +2717,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2781,7 +2778,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2793,7 +2790,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -2810,10 +2807,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2836,13 +2833,13 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2893,7 +2890,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -2922,10 +2919,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2951,10 +2948,10 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3005,7 +3002,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3034,10 +3031,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3060,13 +3057,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3117,7 +3114,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3129,7 +3126,7 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3146,10 +3143,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3172,13 +3169,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3229,25 +3226,25 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3258,14 +3255,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3284,16 +3281,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3343,7 +3340,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3355,13 +3352,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3372,14 +3369,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3398,19 +3395,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3459,7 +3456,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3471,7 +3468,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3488,10 +3485,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3517,10 +3514,10 @@
         <v>81</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3571,7 +3568,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3600,10 +3597,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3629,13 +3626,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3685,7 +3682,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3714,10 +3711,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3740,13 +3737,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3797,7 +3794,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3826,10 +3823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3852,13 +3849,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3909,7 +3906,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3918,7 +3915,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -3938,10 +3935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3964,13 +3961,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4021,25 +4018,25 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4050,14 +4047,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4076,16 +4073,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4135,7 +4132,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4147,13 +4144,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4164,14 +4161,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4190,19 +4187,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4251,7 +4248,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4263,7 +4260,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4280,10 +4277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4309,13 +4306,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4341,14 +4338,14 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4365,7 +4362,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4394,10 +4391,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4420,16 +4417,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4479,7 +4476,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4508,10 +4505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4534,13 +4531,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4591,7 +4588,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4600,7 +4597,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -4620,10 +4617,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4646,13 +4643,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4703,25 +4700,25 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4732,14 +4729,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4758,16 +4755,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4817,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4829,13 +4826,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -4846,14 +4843,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4872,19 +4869,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -4933,7 +4930,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4945,7 +4942,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -4962,10 +4959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4991,10 +4988,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5021,11 +5018,11 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5043,7 +5040,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5072,10 +5069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5101,13 +5098,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5157,7 +5154,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5186,10 +5183,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5212,13 +5209,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5269,7 +5266,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5298,10 +5295,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5324,13 +5321,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5381,7 +5378,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5410,10 +5407,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5436,13 +5433,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5493,7 +5490,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5522,10 +5519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5548,13 +5545,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5605,7 +5602,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5634,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5660,13 +5657,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5717,7 +5714,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5726,7 +5723,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -5746,10 +5743,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5772,13 +5769,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5829,25 +5826,25 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -5858,14 +5855,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5884,16 +5881,16 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5943,7 +5940,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -5955,13 +5952,13 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -5972,14 +5969,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -5998,19 +5995,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6059,7 +6056,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6071,7 +6068,7 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6088,10 +6085,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6114,13 +6111,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6171,7 +6168,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6200,10 +6197,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6229,10 +6226,10 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6283,7 +6280,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6312,10 +6309,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6338,16 +6335,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6397,7 +6394,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6426,10 +6423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6452,16 +6449,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6511,7 +6508,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6540,10 +6537,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6566,16 +6563,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6625,7 +6622,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6654,10 +6651,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6680,19 +6677,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -6741,7 +6738,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>

--- a/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Observation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
